--- a/resultados/matriz_clasificacion_detallada.xlsx
+++ b/resultados/matriz_clasificacion_detallada.xlsx
@@ -436,417 +436,417 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>MAL_MANEJO_CABLES</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MAL_TRATO_FISICO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>MALA_LIMPIEZA_MANTENIMIENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>MAL_TRATO_FISICO</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>MAL_MANEJO_CABLES</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MONITOR DE SIGNOS VITALES</t>
+          <t xml:space="preserve">NEVERA </t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>374</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>660</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICROSCOPIO </t>
+          <t>INCUBADORA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UNIDAD ODONTOLÓGICA</t>
+          <t>TENS</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="C4" t="n">
-        <v>36</v>
-      </c>
-      <c r="D4" t="n">
-        <v>15</v>
-      </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DESFIBRILADOR</t>
+          <t>TERMÓMETRO ELECTRÓNICO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>MANTA TÉRMICA</t>
+          <t>TENSIÓMETRO ANEROIDE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>TENS</t>
+          <t>MÁQUINA DE ANESTESIA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>MESA DE CIRUGÍA</t>
+          <t>MANTA TÉRMICA</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>INCUBADORA</t>
+          <t>ECOTONE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>VENTILADOR ADULTO</t>
+          <t xml:space="preserve">TORRE DE LAPAROSCOPIA </t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" t="n">
         <v>24</v>
       </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TERMÓMETRO</t>
+          <t>DESFIBRILADOR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>TERMOHIGRÓMETRO</t>
+          <t>SUPERFICIE DE AIRE ALTERNANTE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>MÁQUINA DE ANESTESIA</t>
+          <t>HUMIDIFICADOR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
         <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SUPERFICIE DE AIRE ALTERNANTE</t>
+          <t>ELECTROCARDIÓGRAFO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>TERMÓMETRO DE NEVERA DE TRANSPORTE</t>
+          <t xml:space="preserve">REFRIGERADOR </t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">INFUSOR </t>
+          <t xml:space="preserve">MICROSCOPIO </t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>ELECTROENCEFALOGRAFO - POLISOMNÓGRAFO</t>
+          <t xml:space="preserve">FLUJÓMETRO </t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
+        <v>28</v>
+      </c>
+      <c r="E17" t="n">
         <v>11</v>
-      </c>
-      <c r="E17" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>BOMBA DE INFUSIÓN</t>
+          <t>TERMÓMETRO DE NEVERA DE TRANSPORTE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CENTRAL DE MONITOREO</t>
+          <t>TORRE DE ENDOSCOPIA VIDEOGASTROSCOPIO VIDEOCOLONOSCOPIO</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECÓGRAFO </t>
+          <t>TORRE DE ENDOSCOPIA VIDEOBRONCOSCOPIO VIDEODUODENOSCOPIO VIODEOGASTROSCOPIO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>REGULADOR DE VACÍO</t>
+          <t>TORRE DE ENDOSCOPIA VIDEOGASTROSCOPIO VIDEOCOLONOSCOPIO VIDEODUODENO REGULADOR CO2 BOMBA DE IRRIGACIÓN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>HUMIDIFICADOR</t>
+          <t>VENTILADOR ALTA FRECUENCIA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -859,86 +859,86 @@
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>TENSIÓMETRO ANEROIDE</t>
+          <t>TERMOHIGRÓMETRO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>BÁSCULA DIGITAL</t>
+          <t>MONITOR DE SIGNOS VITALES</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>660</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>374</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>TERMÓMETRO ELECTRÓNICO</t>
+          <t>GENERICO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLUJÓMETRO </t>
+          <t xml:space="preserve">INFUSOR </t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E27" t="n">
         <v>6</v>
@@ -947,17 +947,17 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFRIGERADOR </t>
+          <t>ELECTROENCEFALOGRAFO - POLISOMNÓGRAFO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
         <v>8</v>
@@ -966,36 +966,36 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELLADORA </t>
+          <t>VENTILADOR ADULTO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>FONENDOSCOPIO</t>
+          <t>CENTRAL DE MONITOREO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -1011,241 +1011,241 @@
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEVERA </t>
+          <t>BOMBA DE INFUSIÓN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>GENERICO</t>
+          <t>FONENDOSCOPIO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>TORRE DE ENDOSCOPIA VIDEOGASTROSCOPIO VIDEOCOLONOSCOPIO</t>
+          <t xml:space="preserve">ECÓGRAFO </t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
         <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>ELECTROCARDIÓGRAFO</t>
+          <t>CUNA TÉRMICA</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>ECOTONE</t>
+          <t>MESA DE CIRUGÍA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
+        <v>15</v>
+      </c>
+      <c r="D36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E36" t="n">
         <v>2</v>
-      </c>
-      <c r="D36" t="n">
-        <v>14</v>
-      </c>
-      <c r="E36" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRE DE LAPAROSCOPIA </t>
+          <t>REGULADOR DE VACÍO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>TORRE DE ENDOSCOPIA VIDEOGASTROSCOPIO VIDEOCOLONOSCOPIO VIDEODUODENO REGULADOR CO2 BOMBA DE IRRIGACIÓN</t>
+          <t>CAMA ELÉCTRICA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="E38" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>VENTILADOR ALTA FRECUENCIA</t>
+          <t>TERMÓMETRO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>CUNA TÉRMICA</t>
+          <t>AISLADOR ASÉPTICO</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>AISLADOR ASÉPTICO</t>
+          <t>UNIDAD ODONTOLÓGICA</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>TORRE DE ENDOSCOPIA VIDEOBRONCOSCOPIO VIDEODUODENOSCOPIO VIODEOGASTROSCOPIO</t>
+          <t xml:space="preserve">SELLADORA </t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CAMA ELÉCTRICA</t>
+          <t>BÁSCULA DIGITAL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>98</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
